--- a/5_simulation/outputs/tables/supplementary/S15_epsilon_constraint_solutions.xlsx
+++ b/5_simulation/outputs/tables/supplementary/S15_epsilon_constraint_solutions.xlsx
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6.67492490099</v>
+        <v>6.68138794627</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>36028.1148419</v>
+        <v>36067.0017954</v>
       </c>
       <c r="L2" t="n">
         <v>10.4504159794</v>
@@ -595,37 +595,37 @@
         <v>135.457345324</v>
       </c>
       <c r="P2" t="n">
-        <v>130.508030708</v>
+        <v>130.648894579</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.9022980441</v>
+        <v>23.9365630662</v>
       </c>
       <c r="R2" t="n">
-        <v>6.67492490099</v>
+        <v>6.68138794627</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78717586295</v>
+        <v>2.7898781223</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12695422752</v>
+        <v>2.0943697486</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.896003615873</v>
+        <v>-0.922722236492</v>
       </c>
       <c r="V2" t="n">
-        <v>89.45654508059999</v>
+        <v>89.4068453631</v>
       </c>
       <c r="W2" t="n">
-        <v>0.298914317208</v>
+        <v>0.326952644652</v>
       </c>
       <c r="X2" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.6645352591e-15</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.392737192127</v>
+        <v>0.392760436286</v>
       </c>
     </row>
     <row r="3">
@@ -638,64 +638,64 @@
         <v>0.01</v>
       </c>
       <c r="C3" t="n">
-        <v>6.68492490099</v>
+        <v>6.69138794627</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009999999999980001</v>
+        <v>0.01</v>
       </c>
       <c r="F3" t="n">
-        <v>99.2845537501</v>
+        <v>99.2843991819</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7763568394e-14</v>
+        <v>-4.79616346638e-14</v>
       </c>
       <c r="H3" t="n">
-        <v>4.53981795695</v>
+        <v>4.53971503614</v>
       </c>
       <c r="I3" t="n">
-        <v>3.81933417993</v>
+        <v>3.81924759298</v>
       </c>
       <c r="J3" t="n">
-        <v>0.196940077972</v>
+        <v>0.196853491026</v>
       </c>
       <c r="K3" t="n">
-        <v>34171.7428933</v>
+        <v>34209.3834468</v>
       </c>
       <c r="L3" t="n">
-        <v>11.03578598</v>
+        <v>11.0355286154</v>
       </c>
       <c r="M3" t="n">
-        <v>88.96421402</v>
+        <v>88.9644713846</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78813975755</v>
+        <v>2.78820296804</v>
       </c>
       <c r="O3" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P3" t="n">
-        <v>130.51330562</v>
+        <v>130.654105387</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.012489018</v>
+        <v>24.0246076361</v>
       </c>
       <c r="R3" t="n">
-        <v>6.68492490099</v>
+        <v>6.69138794627</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78672882467</v>
+        <v>2.78941175864</v>
       </c>
       <c r="T3" t="n">
-        <v>2.13347681811</v>
+        <v>2.10088120621</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.895964465984</v>
+        <v>-0.922683884472</v>
       </c>
       <c r="V3" t="n">
-        <v>88.87117508</v>
+        <v>88.821732727</v>
       </c>
       <c r="W3" t="n">
-        <v>0.301352939953</v>
+        <v>0.33008663827</v>
       </c>
       <c r="X3" t="n">
         <v>8.881784196999999e-16</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.392777304173</v>
+        <v>0.39280043764</v>
       </c>
     </row>
     <row r="4">
@@ -717,73 +717,73 @@
         <v>0.05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.72492490099</v>
+        <v>6.73138794627</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0500000000429</v>
+        <v>0.0500000000137</v>
       </c>
       <c r="F4" t="n">
-        <v>96.4227687476</v>
+        <v>96.42199590840001</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.28581614642e-11</v>
+        <v>-1.37143629786e-11</v>
       </c>
       <c r="H4" t="n">
-        <v>5.78796783907</v>
+        <v>5.78753054084</v>
       </c>
       <c r="I4" t="n">
-        <v>4.86939864323</v>
+        <v>4.86903074564</v>
       </c>
       <c r="J4" t="n">
-        <v>1.24700454127</v>
+        <v>1.24663664368</v>
       </c>
       <c r="K4" t="n">
-        <v>26804.7655128</v>
+        <v>26835.6069153</v>
       </c>
       <c r="L4" t="n">
-        <v>13.9590139697</v>
+        <v>13.9579204584</v>
       </c>
       <c r="M4" t="n">
-        <v>86.0409860303</v>
+        <v>86.0420795416</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55425874793</v>
+        <v>3.55452730307</v>
       </c>
       <c r="O4" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P4" t="n">
-        <v>130.52308882</v>
+        <v>130.663395149</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.0921221986</v>
+        <v>24.1042408168</v>
       </c>
       <c r="R4" t="n">
-        <v>6.72492490103</v>
+        <v>6.73138794628</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7746469649</v>
+        <v>2.77738450661</v>
       </c>
       <c r="T4" t="n">
-        <v>2.10171997655</v>
+        <v>2.06908749944</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.895875011046</v>
+        <v>-0.922602065716</v>
       </c>
       <c r="V4" t="n">
-        <v>85.9479470903</v>
+        <v>85.8993408841</v>
       </c>
       <c r="W4" t="n">
-        <v>0.29346219546</v>
+        <v>0.322404757702</v>
       </c>
       <c r="X4" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.33226762955e-15</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.392938420825</v>
+        <v>0.392961505821</v>
       </c>
     </row>
     <row r="5">
@@ -796,73 +796,73 @@
         <v>0.1</v>
       </c>
       <c r="C5" t="n">
-        <v>6.77492490099</v>
+        <v>6.78138794627</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>92.8455375013</v>
+        <v>92.8439918187</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.50990331349e-14</v>
+        <v>3.5527136788e-14</v>
       </c>
       <c r="H5" t="n">
-        <v>7.520991716</v>
+        <v>7.52109275999</v>
       </c>
       <c r="I5" t="n">
-        <v>6.32738603184</v>
+        <v>6.32747103982</v>
       </c>
       <c r="J5" t="n">
-        <v>2.70499192988</v>
+        <v>2.70507693786</v>
       </c>
       <c r="K5" t="n">
-        <v>20630.0150844</v>
+        <v>20651.7703973</v>
       </c>
       <c r="L5" t="n">
-        <v>17.8747645732</v>
+        <v>17.8750172445</v>
       </c>
       <c r="M5" t="n">
-        <v>82.1252354268</v>
+        <v>82.1249827555</v>
       </c>
       <c r="N5" t="n">
-        <v>4.95710797247</v>
+        <v>4.95704137498</v>
       </c>
       <c r="O5" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P5" t="n">
-        <v>130.534069282</v>
+        <v>130.67347911</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.0023568716</v>
+        <v>24.0143744458</v>
       </c>
       <c r="R5" t="n">
-        <v>6.77492490099</v>
+        <v>6.78138794627</v>
       </c>
       <c r="S5" t="n">
-        <v>2.80545381277</v>
+        <v>2.80831199843</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04482045849</v>
+        <v>2.01223662583</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.895430116058</v>
+        <v>-0.922153650746</v>
       </c>
       <c r="V5" t="n">
-        <v>82.0321964868</v>
+        <v>81.98224409789999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.278474632981</v>
+        <v>0.304412291836</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784196999999e-16</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.393160522403</v>
+        <v>0.393183827723</v>
       </c>
     </row>
     <row r="6">
@@ -875,28 +875,28 @@
         <v>0.2</v>
       </c>
       <c r="C6" t="n">
-        <v>6.87492490099</v>
+        <v>6.88138794627</v>
       </c>
       <c r="E6" t="n">
-        <v>0.20000000002</v>
+        <v>0.200000000031</v>
       </c>
       <c r="F6" t="n">
-        <v>85.69107500130001</v>
+        <v>85.6879836351</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.97957206183e-11</v>
+        <v>-3.12896375476e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>11.3956483286</v>
+        <v>11.3958113608</v>
       </c>
       <c r="I6" t="n">
-        <v>9.58712212176</v>
+        <v>9.587259280250001</v>
       </c>
       <c r="J6" t="n">
-        <v>5.9647280198</v>
+        <v>5.96486517829</v>
       </c>
       <c r="K6" t="n">
-        <v>13617.5198696</v>
+        <v>13631.7331967</v>
       </c>
       <c r="L6" t="n">
         <v>26.1055177132</v>
@@ -905,34 +905,34 @@
         <v>73.8944822868</v>
       </c>
       <c r="N6" t="n">
-        <v>8.388985047289999</v>
+        <v>8.390295664670001</v>
       </c>
       <c r="O6" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P6" t="n">
-        <v>130.552825985</v>
+        <v>130.690960596</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.0614818495</v>
+        <v>24.0960642796</v>
       </c>
       <c r="R6" t="n">
-        <v>6.87492490101</v>
+        <v>6.8813879463</v>
       </c>
       <c r="S6" t="n">
-        <v>2.87113581962</v>
+        <v>2.87404966323</v>
       </c>
       <c r="T6" t="n">
-        <v>1.90293666778</v>
+        <v>1.87033512266</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.895112256025</v>
+        <v>-0.921840155807</v>
       </c>
       <c r="V6" t="n">
-        <v>73.81492673229999</v>
+        <v>73.7676322854</v>
       </c>
       <c r="W6" t="n">
-        <v>0.252763964586</v>
+        <v>0.273745612789</v>
       </c>
       <c r="X6" t="n">
         <v>8.881784196999999e-16</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.393564597446</v>
+        <v>0.393588012537</v>
       </c>
     </row>
     <row r="7">
@@ -954,28 +954,28 @@
         <v>0.25</v>
       </c>
       <c r="C7" t="n">
-        <v>6.92492490099</v>
+        <v>6.93138794627</v>
       </c>
       <c r="E7" t="n">
         <v>0.25</v>
       </c>
       <c r="F7" t="n">
-        <v>82.1138437533</v>
+        <v>82.1099795467</v>
       </c>
       <c r="G7" t="n">
-        <v>2.93098878501e-14</v>
+        <v>4.70734562441e-14</v>
       </c>
       <c r="H7" t="n">
-        <v>12.4495071374</v>
+        <v>12.4496791885</v>
       </c>
       <c r="I7" t="n">
-        <v>10.4737301328</v>
+        <v>10.4738748789</v>
       </c>
       <c r="J7" t="n">
-        <v>6.85133603084</v>
+        <v>6.85148077691</v>
       </c>
       <c r="K7" t="n">
-        <v>12465.5349825</v>
+        <v>12478.5001346</v>
       </c>
       <c r="L7" t="n">
         <v>28.1227898399</v>
@@ -984,43 +984,43 @@
         <v>71.87721016010001</v>
       </c>
       <c r="N7" t="n">
-        <v>9.664039703129999</v>
+        <v>9.665288121310001</v>
       </c>
       <c r="O7" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P7" t="n">
-        <v>130.560649368</v>
+        <v>130.698249086</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.0519496574</v>
+        <v>24.0640682755</v>
       </c>
       <c r="R7" t="n">
-        <v>6.92492490099</v>
+        <v>6.93138794627</v>
       </c>
       <c r="S7" t="n">
-        <v>2.90931972108</v>
+        <v>2.91224687857</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8502172841</v>
+        <v>1.81763850391</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.894950776441</v>
+        <v>-0.92167971376</v>
       </c>
       <c r="V7" t="n">
-        <v>71.7976546056</v>
+        <v>71.7503601587</v>
       </c>
       <c r="W7" t="n">
-        <v>0.243882204178</v>
+        <v>0.263023468796</v>
       </c>
       <c r="X7" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.11022302463e-15</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.393740220692</v>
+        <v>0.39376354142</v>
       </c>
     </row>
     <row r="8">
@@ -1030,79 +1030,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.349432260001</v>
+        <v>0.349356783371</v>
       </c>
       <c r="C8" t="n">
-        <v>7.02435716099</v>
+        <v>7.03074472964</v>
       </c>
       <c r="D8" t="n">
         <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>0.349432259976</v>
+        <v>0.349356783371</v>
       </c>
       <c r="F8" t="n">
-        <v>75.0000000018</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.47952769428e-11</v>
+        <v>4.08562073062e-14</v>
       </c>
       <c r="H8" t="n">
-        <v>18.6726480163</v>
+        <v>18.6730479116</v>
       </c>
       <c r="I8" t="n">
-        <v>15.7092384485</v>
+        <v>15.7095748791</v>
       </c>
       <c r="J8" t="n">
-        <v>12.0868443465</v>
+        <v>12.0871807771</v>
       </c>
       <c r="K8" t="n">
-        <v>8311.83863455</v>
+        <v>8320.32483793</v>
       </c>
       <c r="L8" t="n">
-        <v>40.9160033242</v>
+        <v>40.9170033053</v>
       </c>
       <c r="M8" t="n">
-        <v>59.0839966758</v>
+        <v>59.0829966947</v>
       </c>
       <c r="N8" t="n">
-        <v>12.3722385716</v>
+        <v>12.3719736122</v>
       </c>
       <c r="O8" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P8" t="n">
-        <v>130.572655056</v>
+        <v>130.70876606</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.9126675996</v>
+        <v>23.9247862178</v>
       </c>
       <c r="R8" t="n">
-        <v>7.02435716096</v>
+        <v>7.03074472964</v>
       </c>
       <c r="S8" t="n">
-        <v>3.01495011878</v>
+        <v>3.01792339954</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73866055744</v>
+        <v>1.70618434788</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.894467457796</v>
+        <v>-0.9211970259509999</v>
       </c>
       <c r="V8" t="n">
-        <v>59.1110218044</v>
+        <v>59.0627273764</v>
       </c>
       <c r="W8" t="n">
-        <v>0.217743574004</v>
+        <v>0.230758646255</v>
       </c>
       <c r="X8" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.33226762955e-15</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.394274324327</v>
+        <v>0.394297711901</v>
       </c>
     </row>
     <row r="9">
@@ -1115,73 +1115,73 @@
         <v>0.5</v>
       </c>
       <c r="C9" t="n">
-        <v>7.17492490099</v>
+        <v>7.18138794627</v>
       </c>
       <c r="E9" t="n">
-        <v>0.499999999997</v>
+        <v>0.500000000006</v>
       </c>
       <c r="F9" t="n">
-        <v>64.2276875069</v>
+        <v>64.2199590929</v>
       </c>
       <c r="G9" t="n">
-        <v>2.51887399827e-12</v>
+        <v>-6.433076293890001e-12</v>
       </c>
       <c r="H9" t="n">
-        <v>27.0457419111</v>
+        <v>27.0501990187</v>
       </c>
       <c r="I9" t="n">
-        <v>22.7534952904</v>
+        <v>22.7572450406</v>
       </c>
       <c r="J9" t="n">
-        <v>19.1311011884</v>
+        <v>19.1348509386</v>
       </c>
       <c r="K9" t="n">
-        <v>5739.34959838</v>
+        <v>5744.27240805</v>
       </c>
       <c r="L9" t="n">
-        <v>55.2312978903</v>
+        <v>55.2411445493</v>
       </c>
       <c r="M9" t="n">
-        <v>44.7687021097</v>
+        <v>44.7588554507</v>
       </c>
       <c r="N9" t="n">
-        <v>18.334096305</v>
+        <v>18.332995503</v>
       </c>
       <c r="O9" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P9" t="n">
-        <v>130.590264057</v>
+        <v>130.72381477</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.9936653637</v>
+        <v>24.0221990101</v>
       </c>
       <c r="R9" t="n">
-        <v>7.17492490098</v>
+        <v>7.18138794627</v>
       </c>
       <c r="S9" t="n">
-        <v>3.14812666903</v>
+        <v>3.15122304757</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49067623615</v>
+        <v>1.45831548537</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.893987737852</v>
+        <v>-0.920723601588</v>
       </c>
       <c r="V9" t="n">
-        <v>45.0836205281</v>
+        <v>45.0264794222</v>
       </c>
       <c r="W9" t="n">
-        <v>0.201046648608</v>
+        <v>0.203314556304</v>
       </c>
       <c r="X9" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784196999999e-16</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.394942934189</v>
+        <v>0.394966586052</v>
       </c>
     </row>
     <row r="10">
@@ -1191,79 +1191,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6988645200019999</v>
+        <v>0.698713566741</v>
       </c>
       <c r="C10" t="n">
-        <v>7.37378942099</v>
+        <v>7.38010151301</v>
       </c>
       <c r="D10" t="n">
         <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6988645200019999</v>
+        <v>0.698713566741</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.15463194561e-14</v>
+        <v>-1.38555833473e-13</v>
       </c>
       <c r="H10" t="n">
-        <v>43.1685299499</v>
+        <v>43.1640075441</v>
       </c>
       <c r="I10" t="n">
-        <v>36.3175447779</v>
+        <v>36.3137400925</v>
       </c>
       <c r="J10" t="n">
-        <v>32.695150676</v>
+        <v>32.6913459906</v>
       </c>
       <c r="K10" t="n">
-        <v>3595.668362</v>
+        <v>3599.57633632</v>
       </c>
       <c r="L10" t="n">
-        <v>75.8412608014</v>
+        <v>75.83852669780001</v>
       </c>
       <c r="M10" t="n">
-        <v>24.1587391986</v>
+        <v>24.1614733022</v>
       </c>
       <c r="N10" t="n">
-        <v>29.7424975281</v>
+        <v>29.7376695387</v>
       </c>
       <c r="O10" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P10" t="n">
-        <v>130.585846743</v>
+        <v>130.71407952</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.062181801</v>
+        <v>24.0975977155</v>
       </c>
       <c r="R10" t="n">
-        <v>7.37378942099</v>
+        <v>7.38010151301</v>
       </c>
       <c r="S10" t="n">
-        <v>3.31502891346</v>
+        <v>3.31803360831</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01493598662</v>
+        <v>0.982921429261</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.893029122766</v>
+        <v>-0.919772517697</v>
       </c>
       <c r="V10" t="n">
-        <v>27.6624470901</v>
+        <v>27.8347238926</v>
       </c>
       <c r="W10" t="n">
-        <v>0.172889227356</v>
+        <v>0.167713125698</v>
       </c>
       <c r="X10" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.7763568394e-15</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.395998356593</v>
+        <v>0.396021374406</v>
       </c>
     </row>
     <row r="11">
@@ -1276,28 +1276,28 @@
         <v>0.75</v>
       </c>
       <c r="C11" t="n">
-        <v>7.42492490099</v>
+        <v>7.43138794627</v>
       </c>
       <c r="E11" t="n">
-        <v>0.750000000038</v>
+        <v>0.75</v>
       </c>
       <c r="F11" t="n">
-        <v>46.3415312573</v>
+        <v>46.3299386401</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.79527520522e-11</v>
+        <v>-1.7763568394e-14</v>
       </c>
       <c r="H11" t="n">
-        <v>48.774678887</v>
+        <v>48.7788287777</v>
       </c>
       <c r="I11" t="n">
-        <v>41.0339797663</v>
+        <v>41.0374710559</v>
       </c>
       <c r="J11" t="n">
-        <v>37.4115856644</v>
+        <v>37.415076954</v>
       </c>
       <c r="K11" t="n">
-        <v>3182.28716003</v>
+        <v>3185.1042489</v>
       </c>
       <c r="L11" t="n">
         <v>81.8516011964</v>
@@ -1306,43 +1306,43 @@
         <v>18.1483988036</v>
       </c>
       <c r="N11" t="n">
-        <v>32.890008559</v>
+        <v>32.8957179853</v>
       </c>
       <c r="O11" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P11" t="n">
-        <v>130.581906935</v>
+        <v>130.708623424</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.0780374916</v>
+        <v>24.0900866166</v>
       </c>
       <c r="R11" t="n">
-        <v>7.42492490102</v>
+        <v>7.43138794627</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35407550338</v>
+        <v>3.35717523004</v>
       </c>
       <c r="T11" t="n">
-        <v>0.883566141584</v>
+        <v>0.851176476334</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.892779219278</v>
+        <v>-0.9195233259359999</v>
       </c>
       <c r="V11" t="n">
-        <v>24.4120397206</v>
+        <v>24.6584309105</v>
       </c>
       <c r="W11" t="n">
-        <v>0.165957937054</v>
+        <v>0.157783246758</v>
       </c>
       <c r="X11" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.6645352591e-15</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.396261311108</v>
+        <v>0.396284932494</v>
       </c>
     </row>
     <row r="12">
@@ -1355,28 +1355,28 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>7.67492490099</v>
+        <v>7.68138794627</v>
       </c>
       <c r="E12" t="n">
-        <v>0.999999999999</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>28.4553750134</v>
+        <v>28.4399181867</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6221693967e-13</v>
+        <v>-1.56141766183e-12</v>
       </c>
       <c r="H12" t="n">
-        <v>87.06473425119999</v>
+        <v>87.07299376260001</v>
       </c>
       <c r="I12" t="n">
-        <v>73.2472796366</v>
+        <v>73.2542283369</v>
       </c>
       <c r="J12" t="n">
-        <v>69.6248855347</v>
+        <v>69.6318342349</v>
       </c>
       <c r="K12" t="n">
-        <v>1781.42359308</v>
+        <v>1782.80925862</v>
       </c>
       <c r="L12" t="n">
         <v>99.3404839506</v>
@@ -1385,43 +1385,43 @@
         <v>0.659516049365</v>
       </c>
       <c r="N12" t="n">
-        <v>54.3712664006</v>
+        <v>54.3755946203</v>
       </c>
       <c r="O12" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P12" t="n">
-        <v>130.484432073</v>
+        <v>130.598316512</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.3592374199</v>
+        <v>24.3937976473</v>
       </c>
       <c r="R12" t="n">
-        <v>7.67492490099</v>
+        <v>7.68138794627</v>
       </c>
       <c r="S12" t="n">
-        <v>3.52633115998</v>
+        <v>3.52947561676</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0144558200833</v>
+        <v>-0.0462996048992</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.891259491871</v>
+        <v>-0.918013026927</v>
       </c>
       <c r="V12" t="n">
-        <v>37.9239402028</v>
+        <v>39.1427780416</v>
       </c>
       <c r="W12" t="n">
-        <v>0.152434837155</v>
+        <v>0.129934140854</v>
       </c>
       <c r="X12" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784196999999e-16</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.398005082704</v>
+        <v>0.39802879597</v>
       </c>
     </row>
     <row r="13">
@@ -1431,34 +1431,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.04829678</v>
+        <v>1.04807035011</v>
       </c>
       <c r="C13" t="n">
-        <v>7.72322168099</v>
+        <v>7.72945829638</v>
       </c>
       <c r="D13" t="n">
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>1.04829678</v>
+        <v>1.04807035011</v>
       </c>
       <c r="F13" t="n">
-        <v>25.0000000003</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.78896913844e-12</v>
+        <v>2.75335310107e-13</v>
       </c>
       <c r="H13" t="n">
-        <v>99.4221614991</v>
+        <v>99.36838100759999</v>
       </c>
       <c r="I13" t="n">
-        <v>83.6435432559</v>
+        <v>83.5982979021</v>
       </c>
       <c r="J13" t="n">
-        <v>80.0211491539</v>
+        <v>79.9759038001</v>
       </c>
       <c r="K13" t="n">
-        <v>1559.12402483</v>
+        <v>1561.26232436</v>
       </c>
       <c r="L13" t="n">
         <v>100</v>
@@ -1467,43 +1467,43 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>59.7772998003</v>
+        <v>59.7555303344</v>
       </c>
       <c r="O13" t="n">
         <v>135.457345324</v>
       </c>
       <c r="P13" t="n">
-        <v>130.410657812</v>
+        <v>130.518872895</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.4413624382</v>
+        <v>24.4534723931</v>
       </c>
       <c r="R13" t="n">
-        <v>7.72322168099</v>
+        <v>7.72945829638</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55742867637</v>
+        <v>3.56043737233</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.240539633503</v>
+        <v>-0.271157016933</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.89068458898</v>
+        <v>-0.917445058941</v>
       </c>
       <c r="V13" t="n">
-        <v>46.5947976525</v>
+        <v>47.9605043431</v>
       </c>
       <c r="W13" t="n">
-        <v>0.146579666254</v>
+        <v>0.127964972542</v>
       </c>
       <c r="X13" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.6645352591e-15</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.39860721862</v>
+        <v>0.398627054929</v>
       </c>
     </row>
     <row r="14">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.05030785108</v>
+        <v>1.05026959238</v>
       </c>
       <c r="C14" t="n">
-        <v>7.72523275207</v>
+        <v>7.73165753865</v>
       </c>
       <c r="E14" t="n">
-        <v>1.05030785108</v>
+        <v>1.05026959239</v>
       </c>
       <c r="F14" t="n">
-        <v>24.8561186738</v>
+        <v>24.8426220428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.56408219709e-12</v>
+        <v>-4.854783242080001e-12</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -1537,7 +1537,7 @@
         <v>80.50728281790001</v>
       </c>
       <c r="K14" t="n">
-        <v>1550.06610902</v>
+        <v>1551.34321431</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -1552,37 +1552,37 @@
         <v>135.457345324</v>
       </c>
       <c r="P14" t="n">
-        <v>130.406560957</v>
+        <v>130.514003412</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.4413624382</v>
+        <v>24.4534723931</v>
       </c>
       <c r="R14" t="n">
-        <v>7.72523275207</v>
+        <v>7.73165753865</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55872365005</v>
+        <v>3.56185401718</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.250257235465</v>
+        <v>-0.281778329406</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.890668060596</v>
+        <v>-0.917424874381</v>
       </c>
       <c r="V14" t="n">
-        <v>47.2118384312</v>
+        <v>48.170269522</v>
       </c>
       <c r="W14" t="n">
-        <v>0.146145315866</v>
+        <v>0.127399663451</v>
       </c>
       <c r="X14" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784196999999e-16</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.398637349043</v>
+        <v>0.398660356811</v>
       </c>
     </row>
   </sheetData>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recipients in excess of the 4.3057268666% minimum-gap design. Negative values denote smaller coverage.</t>
+          <t>Recipients in excess of the numerically selected minimum-gap design. Negative values denote smaller coverage.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
